--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/post DDV_HRM-2031-0420/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.0154</v>
+        <v>16.98304</v>
       </c>
       <c r="D2" t="n">
-        <v>16.63206</v>
+        <v>16.34437</v>
       </c>
       <c r="E2" t="n">
-        <v>16.60677</v>
+        <v>16.91965</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52002</v>
+        <v>42.63965</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04981</v>
+        <v>0.0518</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85417</v>
+        <v>1.82658</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.17636</v>
+        <v>16.88567</v>
       </c>
       <c r="D3" t="n">
-        <v>16.80517</v>
+        <v>16.56605</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89248</v>
+        <v>16.62369</v>
       </c>
       <c r="F3" t="n">
-        <v>43.15722</v>
+        <v>43.27039</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05233</v>
+        <v>0.05125</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80409</v>
+        <v>1.80071</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.22061</v>
+        <v>17.00002</v>
       </c>
       <c r="D4" t="n">
-        <v>16.77314</v>
+        <v>16.68456</v>
       </c>
       <c r="E4" t="n">
-        <v>17.08397</v>
+        <v>16.91421</v>
       </c>
       <c r="F4" t="n">
-        <v>43.80923</v>
+        <v>42.52745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05135</v>
+        <v>0.05133</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87457</v>
+        <v>1.82239</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.85086</v>
+        <v>16.8411</v>
       </c>
       <c r="D6" t="n">
-        <v>15.89439</v>
+        <v>16.37063</v>
       </c>
       <c r="E6" t="n">
-        <v>16.72323</v>
+        <v>16.8083</v>
       </c>
       <c r="F6" t="n">
-        <v>22.08779</v>
+        <v>22.28096</v>
       </c>
       <c r="G6" t="n">
-        <v>34.65201</v>
+        <v>34.16994</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.90734</v>
+        <v>17.03451</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00973</v>
+        <v>16.05091</v>
       </c>
       <c r="E7" t="n">
-        <v>16.58499</v>
+        <v>17.00408</v>
       </c>
       <c r="F7" t="n">
-        <v>22.27822</v>
+        <v>21.79967</v>
       </c>
       <c r="G7" t="n">
-        <v>34.14675</v>
+        <v>34.69369</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.81566</v>
+        <v>16.85221</v>
       </c>
       <c r="D8" t="n">
-        <v>16.18312</v>
+        <v>16.22138</v>
       </c>
       <c r="E8" t="n">
-        <v>16.71235</v>
+        <v>16.79941</v>
       </c>
       <c r="F8" t="n">
-        <v>22.23171</v>
+        <v>22.00264</v>
       </c>
       <c r="G8" t="n">
-        <v>34.31536</v>
+        <v>33.97078</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61329</v>
+        <v>0.60765</v>
       </c>
       <c r="D10" t="n">
-        <v>1.12167</v>
+        <v>1.12589</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60286</v>
+        <v>0.6196700000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12447</v>
+        <v>1.10867</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60411</v>
+        <v>0.5996</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1392</v>
+        <v>1.11316</v>
       </c>
     </row>
   </sheetData>
